--- a/variants/results/summary_grid.xlsx
+++ b/variants/results/summary_grid.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary grid" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Headlines" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary grid" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Definitions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -78,8 +79,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -467,7 +471,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="120" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BGN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>regime-g extreme (g0235)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flagship</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Gap +0.030 vs best linear, +0.108 vs FMR (t=29, 160% relative). Regime-whipsawed levels break FMR/FF/linlev; DKKM's rank features are immune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>priced-vol extreme (vyx)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flagship</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Room +0.350 and capture ~29%: gap +0.101 vs best linear, +0.108 vs FMR (t=21.6). The data-magnitude win - premium-side extremity raises room AND capture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>exposure-types wide (bx7)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flagship</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Gap +0.016 vs FMR (t=10.4), ~1:1 harvest of the +0.018 room; ranks+levels linear ridge comes within 0.001. GS's harvestable optimum - pushing further (bx9) triples room but capture collapses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>law</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Realized gap = room x capture. Premium-side extremity (bigger priced exposure spreads) raises both. Volatility-side extremity either breaks the classical methods (BGN: relative gap explodes) or breaks theta estimation itself (GS bx9: gap vanishes). All three models need the same ingredient the published versions lack: heterogeneous firm-level exposures bent nonlinearly by an aggregate state, confined to rank/interaction space.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -486,1056 +608,1197 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>variant</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>SR_max</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lin_ceil</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>nl_ceil</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>room</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>FMR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>FF</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>lin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>RFF</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>gap_RFF-lin</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>t_vs_FMR</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>BGN</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>0.2926449433091425</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.2346732705250239</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.2711594898719345</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>0.03648621934691057</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="F2" s="4" t="n">
+        <v>0.0364862193469105</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.2197661746329787</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.2201764268011541</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>0.2333813786869419</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>0.2392569374164523</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>0.005875558729510399</v>
-      </c>
-      <c r="L2" s="3" t="n">
+      <c r="K2" s="4" t="n">
+        <v>0.0058755587295103</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>14.00767899222574</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>BGN 1999 exactly as published (paper Table I calibration), rank chars, unpenalized market.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BGN</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>crash</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0.3683664515412792</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" s="4" t="n">
+        <v>0.3683664515412791</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>0.2627233298677992</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.3285277879179037</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.06580445805010449</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="F3" s="4" t="n">
+        <v>0.0658044580501044</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>0.2482545178913427</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>0.2415771199452922</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>0.2546513220040536</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>0.2599832040451561</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>0.00533188204110252</v>
-      </c>
-      <c r="L3" s="3" t="n">
+      <c r="K3" s="4" t="n">
+        <v>0.0053318820411025</v>
+      </c>
+      <c r="L3" s="4" t="n">
         <v>8.932455365295723</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Rare-disaster kernel (lognormal x kappa^D), disaster-exposure project types, priced survival, compensation omega=1.3, level features.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>BGN</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>regime-g</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0.2450497543300507</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="4" t="n">
+        <v>0.2450497543300506</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>0.1955563204270897</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.2169264096510296</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0.02137008922393993</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="F4" s="4" t="n">
+        <v>0.0213700892239399</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>0.2164279427020741</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>0.2189645878271004</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <v>0.2199847126090859</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="4" t="n">
         <v>0.2418767154671829</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <v>0.021892002858097</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>21.52273267407994</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>2-state observable regime multiplying the price of risk gamma by [0.5, 2.0]; closed-form two-basis valuation; regime exported as conditioning feature.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>BGN</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>regime-g wide</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.2121944389641843</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="4" t="n">
+        <v>0.2121944389641842</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>0.1542661426890018</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.1796934258285182</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0.02542728313951639</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="F5" s="4" t="n">
+        <v>0.0254272831395163</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.105239894544284</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.1315725354102601</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>0.1744616206237873</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <v>0.1984714507250376</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.0240098301012503</v>
-      </c>
-      <c r="L5" s="3" t="n">
+      <c r="K5" s="4" t="n">
+        <v>0.0240098301012502</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>31.67276893879778</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Same regime-gamma design with wide multipliers [0.3, 3.0]; regime-shifting char levels break rolling FMR/FF.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>0.2396177255291423</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>0.2225978217902375</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="7" t="n">
+        <v>0.2225978217902374</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>0.2263054653282818</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>0.00370764353804437</v>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="F6" s="7" t="n">
+        <v>0.0037076435380443</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>0.2052435245721245</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>0.1926421040772017</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.1968873025669739</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <v>0.2005246857225434</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <v>0.003637383155569496</v>
-      </c>
-      <c r="L6" s="6" t="n">
+      <c r="K6" s="7" t="n">
+        <v>0.0036373831555694</v>
+      </c>
+      <c r="L6" s="7" t="n">
         <v>-8.521358384545877</v>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>KP14 as published (paper Table II calibration; r=5% as in Code/), rank chars, unpenalized market.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>crash</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>0.3501414633107325</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>0.3277868895318069</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>0.3336024846408646</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>0.005815595109057714</v>
-      </c>
-      <c r="G7" s="6" t="n">
+      <c r="F7" s="7" t="n">
+        <v>0.0058155951090577</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>0.3007318305304302</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>0.2953582130310255</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.3039185979764888</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="7" t="n">
         <v>0.2975248926962616</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>-0.006393705280227202</v>
-      </c>
-      <c r="L7" s="6" t="n">
+      <c r="K7" s="7" t="n">
+        <v>-0.0063937052802272</v>
+      </c>
+      <c r="L7" s="7" t="n">
         <v>-2.13472135888646</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Disaster recipe ported to KP14: kernel x kappa^D, exposure-typed project kill fractions, priced survival, compensation.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>regime-g</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>0.250947026700919</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>0.2217417372659605</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>0.2232823944672129</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>0.001540657201252377</v>
-      </c>
-      <c r="G8" s="6" t="n">
+      <c r="E8" s="7" t="n">
+        <v>0.2232823944672128</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0.0015406572012523</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>0.1624971958886369</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>0.1707805445014819</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>0.1682548907862677</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="7" t="n">
         <v>0.1749717149224474</v>
       </c>
-      <c r="K8" s="6" t="n">
-        <v>0.006716824136179689</v>
-      </c>
-      <c r="L8" s="6" t="n">
+      <c r="K8" s="7" t="n">
+        <v>0.0067168241361796</v>
+      </c>
+      <c r="L8" s="7" t="n">
         <v>5.124594571926351</v>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>2-state regime multiplying both prices of risk (gamma_x, gamma_z) by [0.5, 2.0]; coupled A-coefficients and 4-state G tables.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>0.4011672037186064</v>
-      </c>
-      <c r="D9" s="9" t="n">
+      <c r="C9" s="10" t="n">
+        <v>0.4011672037186063</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>0.399550571019955</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.4005998583091442</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>0.001049287289189238</v>
-      </c>
-      <c r="G9" s="9" t="n">
+      <c r="F9" s="10" t="n">
+        <v>0.0010492872891892</v>
+      </c>
+      <c r="G9" s="10" t="n">
         <v>0.378520931822595</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>0.3715760591110675</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <v>0.3825383603538805</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="10" t="n">
         <v>0.3987919382965892</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>0.01625357794270871</v>
-      </c>
-      <c r="L9" s="9" t="n">
+      <c r="K9" s="10" t="n">
+        <v>0.0162535779427087</v>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>21.82069527961823</v>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>GS21 with the exact-kernel Python re-solve (row-renormalized SDF, converged fixed point), constant gamma_x=0.5.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>crash</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.4134233839587583</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>0.4057636424768657</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>0.4122751531910753</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <v>0.006511510714209634</v>
-      </c>
-      <c r="G10" s="9" t="n">
+      <c r="F10" s="10" t="n">
+        <v>0.0065115107142096</v>
+      </c>
+      <c r="G10" s="10" t="n">
         <v>0.3805130631792924</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="10" t="n">
         <v>0.3733330386985705</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <v>0.3797970693689025</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="10" t="n">
         <v>0.3883540691784674</v>
       </c>
-      <c r="K10" s="9" t="n">
-        <v>0.008556999809564869</v>
-      </c>
-      <c r="L10" s="9" t="n">
+      <c r="K10" s="10" t="n">
+        <v>0.0085569998095648</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>5.054533819094187</v>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Disaster recipe in GS (re-based on exact kernel): kernel x kappa^D, capital-destruction types, endogenous deleveraging and real defaults.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>gamma(x)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.3604977508766891</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>0.3588058891346375</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="10" t="n">
+        <v>0.3588058891346374</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>0.3583854128664749</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>-0.0004204762681625507</v>
-      </c>
-      <c r="G11" s="9" t="n">
+      <c r="F11" s="10" t="n">
+        <v>-0.0004204762681625</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>0.3162945879530055</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="10" t="n">
         <v>0.3239479050356987</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="10" t="n">
         <v>0.3197503182136805</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="10" t="n">
         <v>0.358079986889338</v>
       </c>
-      <c r="K11" s="9" t="n">
-        <v>0.03832966867565751</v>
-      </c>
-      <c r="L11" s="9" t="n">
+      <c r="K11" s="10" t="n">
+        <v>0.0383296686756575</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>17.92451112313196</v>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>State-dependent price of risk gamma(x) = clip(0.5 - 0.28 x/sd, 0.05, 1), re-solved value functions; conditioning/timing channel only.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>BGN</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>gamma(r) nonlin</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.5566768613896587</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>0.439210129809596</v>
-      </c>
-      <c r="E12" s="3" t="n">
+      <c r="D12" s="4" t="n">
+        <v>0.4392101298095959</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>0.5326448729566664</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>0.09343474314707045</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="4" t="n">
+        <v>0.0934347431470704</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>0.4697801897276737</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.4150581418173273</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>0.4584038411581797</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="4" t="n">
         <v>0.4643697058800507</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>0.005965864721870995</v>
-      </c>
-      <c r="L12" s="3" t="n">
+      <c r="K12" s="4" t="n">
+        <v>0.0059658647218709</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>-2.68339795898713</v>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>gamma = smooth logistic function of the interest rate r (continuous observable state, 0.5-3.0); operator-chain pricing on an r-grid.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>gamma(x) nonlin</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>0.3979986642374948</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="10" t="n">
         <v>0.3954969849209439</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>0.3950058978379418</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>-0.0004910870830021619</v>
-      </c>
-      <c r="G13" s="9" t="n">
+      <c r="E13" s="10" t="n">
+        <v>0.3950058978379417</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>-0.0004910870830021</v>
+      </c>
+      <c r="G13" s="10" t="n">
         <v>0.3490234464008104</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="10" t="n">
         <v>0.35767684784622</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10" t="n">
         <v>0.3511326060555419</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="10" t="n">
         <v>0.3916894444532564</v>
       </c>
-      <c r="K13" s="9" t="n">
-        <v>0.04055683839771446</v>
-      </c>
-      <c r="L13" s="9" t="n">
+      <c r="K13" s="10" t="n">
+        <v>0.0405568383977144</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>14.0532293244742</v>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Logistic (strongly nonlinear) gamma(x); still zero cross-sectional room - direction-invariance theorem.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>gamma(y) common</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>0.3657272945742748</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>0.3404526090217086</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>0.3437483237782333</v>
       </c>
-      <c r="F14" s="6" t="n">
-        <v>0.003295714756524737</v>
-      </c>
-      <c r="G14" s="6" t="n">
+      <c r="F14" s="7" t="n">
+        <v>0.0032957147565247</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>0.2788622792327486</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>0.2766144703519655</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>0.2739306113856559</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>0.2813492199761638</v>
       </c>
-      <c r="K14" s="6" t="n">
-        <v>0.007418608590507914</v>
-      </c>
-      <c r="L14" s="6" t="n">
+      <c r="K14" s="7" t="n">
+        <v>0.0074186085905079</v>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>3.049470194536278</v>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>gamma multiplier = smooth function of a continuous OU state y, common to both shocks (21-node y-grid, GH quadrature mixing).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>gamma(y) rotation</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>0.4300969430628008</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>0.4141345432107322</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>0.4176399640543538</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>0.003505420843621543</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="F15" s="7" t="n">
+        <v>0.0035054208436215</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>0.3634085047724382</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>0.3454655370151073</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>0.3643993476816265</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="7" t="n">
         <v>0.3666443416408312</v>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>0.002244993959204689</v>
-      </c>
-      <c r="L15" s="6" t="n">
+      <c r="K15" s="7" t="n">
+        <v>0.0022449939592046</v>
+      </c>
+      <c r="L15" s="7" t="n">
         <v>4.734755598155505</v>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>gamma_x varies with y (0.85-3.0) while gamma_z stays fixed - a rotation of the price-of-risk vector, not a rescaling.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>regime uneven</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>0.2941226903157696</v>
       </c>
-      <c r="D16" s="6" t="n">
-        <v>0.2675985958420045</v>
-      </c>
-      <c r="E16" s="6" t="n">
+      <c r="D16" s="7" t="n">
+        <v>0.2675985958420044</v>
+      </c>
+      <c r="E16" s="7" t="n">
         <v>0.2700903031132479</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>0.002491707271243426</v>
-      </c>
-      <c r="G16" s="6" t="n">
+      <c r="F16" s="7" t="n">
+        <v>0.0024917072712434</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>0.207252045033287</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>0.2122063427575118</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>0.2075523834200544</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="7" t="n">
         <v>0.2260700787202717</v>
       </c>
-      <c r="K16" s="6" t="n">
-        <v>0.01851769530021732</v>
-      </c>
-      <c r="L16" s="6" t="n">
+      <c r="K16" s="7" t="n">
+        <v>0.0185176953002173</v>
+      </c>
+      <c r="L16" s="7" t="n">
         <v>9.616719409966588</v>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>2-state regime scaling gamma_x only (x-channel swing), leaving gamma_z fixed - uneven version of regime-g.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>regime-g</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <v>0.2167335484468557</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="10" t="n">
         <v>0.215861787109518</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>0.2159204706539665</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>5.868354444851787e-05</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="10" t="n">
         <v>0.1753501576690034</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="10" t="n">
         <v>0.1727542441163332</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <v>0.1760916004774309</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="10" t="n">
         <v>0.1948347841366278</v>
       </c>
-      <c r="K17" s="9" t="n">
-        <v>0.01874318365919692</v>
-      </c>
-      <c r="L17" s="9" t="n">
+      <c r="K17" s="10" t="n">
+        <v>0.0187431836591969</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>19.88007901688635</v>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>2-regime gamma multiplier [0.6, 3.0] with coupled 2-regime solver; timing gap without cross-sectional room.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>exposure-types x regime</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>0.2768819037518112</v>
-      </c>
-      <c r="D18" s="6" t="n">
+      <c r="C18" s="7" t="n">
+        <v>0.2768819037518111</v>
+      </c>
+      <c r="D18" s="7" t="n">
         <v>0.2394146343640208</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>0.2580941276221579</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>0.01867949325813714</v>
-      </c>
-      <c r="G18" s="6" t="n">
+      <c r="F18" s="7" t="n">
+        <v>0.0186794932581371</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>0.1809047814981866</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>0.0975457758123192</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>0.1753502899803655</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="7" t="n">
         <v>0.1769522673499174</v>
       </c>
-      <c r="K18" s="6" t="n">
-        <v>0.001601977369551894</v>
-      </c>
-      <c r="L18" s="6" t="n">
+      <c r="K18" s="7" t="n">
+        <v>0.0016019773695518</v>
+      </c>
+      <c r="L18" s="7" t="n">
         <v>-1.823937925390352</v>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>Firm types load cash flows as x^beta (beta 1.0/1.8/3.0, GBM powers closed-form) crossed with regime-gamma [0.5,2] + calm-value compensation 1.2. First KP room; not harvested (exposure leaks into raw char levels, rolling FMR conditions on them).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>exposure-types x regime</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <v>0.2619526952294413</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <v>0.2512246404491086</v>
       </c>
-      <c r="E19" s="9" t="n">
-        <v>0.255077997146027</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.003853356696918386</v>
-      </c>
-      <c r="G19" s="9" t="n">
+      <c r="E19" s="10" t="n">
+        <v>0.2550779971460269</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.0038533566969183</v>
+      </c>
+      <c r="G19" s="10" t="n">
         <v>0.2132470229423955</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="10" t="n">
         <v>0.2147201048226968</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10" t="n">
         <v>0.2185106670301823</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="10" t="n">
         <v>0.2225198690631823</v>
       </c>
-      <c r="K19" s="9" t="n">
-        <v>0.004009202033000009</v>
-      </c>
-      <c r="L19" s="9" t="n">
+      <c r="K19" s="10" t="n">
+        <v>0.004009202033</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>10.78895850569168</v>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Firm types with heterogeneous production exposure e^{beta x} (3 types) crossed with regime-gamma [0.6,3.0].</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>exposure-types comp.</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <v>0.2708250257365746</v>
       </c>
-      <c r="D20" s="9" t="n">
-        <v>0.2554903205364624</v>
-      </c>
-      <c r="E20" s="9" t="n">
+      <c r="D20" s="10" t="n">
+        <v>0.2554903205364623</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>0.2619046538288476</v>
       </c>
-      <c r="F20" s="9" t="n">
-        <v>0.006414333292385277</v>
-      </c>
-      <c r="G20" s="9" t="n">
+      <c r="F20" s="10" t="n">
+        <v>0.0064143332923852</v>
+      </c>
+      <c r="G20" s="10" t="n">
         <v>0.2086181838812497</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="10" t="n">
         <v>0.2245537627863333</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="10" t="n">
         <v>0.2235335940986725</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="10" t="n">
         <v>0.2257475366497142</v>
       </c>
-      <c r="K20" s="9" t="n">
-        <v>0.002213942551041709</v>
-      </c>
-      <c r="L20" s="9" t="n">
+      <c r="K20" s="10" t="n">
+        <v>0.0022139425510417</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>16.75356404920559</v>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>Same exposure types + calm-value compensation (a-shifts dosed from measured calm log-value gaps) so values do not reveal types monotonically.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>KP</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>priced-vol exposures (vy)</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>0.9608773449056806</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>0.5392151250539609</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>0.8174862562284813</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.2782711311745204</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>0.5448986908546309</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>0.45605960273786</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.5417129502158761</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>0.5706576041682037</v>
       </c>
-      <c r="K21" s="6" t="n">
-        <v>0.02894465395232759</v>
-      </c>
-      <c r="L21" s="6" t="n">
+      <c r="K21" s="7" t="n">
+        <v>0.0289446539523275</v>
+      </c>
+      <c r="L21" s="7" t="n">
         <v>5.18326185620934</v>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>Priced stationary OU factor y (kappa=0.35, gamma_v=1.2); types load e^{beta y} (beta 0.02/0.06/0.12, premia 2-12%/yr) + y=0 compensation 1.2. Levels stationary by design. Largest room of the project (+0.28); harvested: rff_ens beats FMR by +0.026 (t=5.2).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>exposure-types wide (bx7)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>0.2989286581126623</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>0.2739047029520214</v>
-      </c>
-      <c r="E22" s="9" t="n">
+      <c r="D22" s="10" t="n">
+        <v>0.2739047029520213</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>0.2920884231322297</v>
       </c>
-      <c r="F22" s="9" t="n">
-        <v>0.01818372018020836</v>
-      </c>
-      <c r="G22" s="9" t="n">
+      <c r="F22" s="10" t="n">
+        <v>0.0181837201802083</v>
+      </c>
+      <c r="G22" s="10" t="n">
         <v>0.2213462414449939</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="10" t="n">
         <v>0.2290612238210095</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="10" t="n">
         <v>0.2355676413532739</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="10" t="n">
         <v>0.2368987872115804</v>
       </c>
-      <c r="K22" s="9" t="n">
-        <v>0.001331145858306487</v>
-      </c>
-      <c r="L22" s="9" t="n">
+      <c r="K22" s="10" t="n">
+        <v>0.0013311458583064</v>
+      </c>
+      <c r="L22" s="10" t="n">
         <v>10.44650856554889</v>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>5 types, beta 1-7, compensation dosed by value-gap slope, leverage characteristic added. Room +0.018, harvested vs classical methods: rff beats FMR by +0.016 (t=10.4); linear ranks+levels ridge comes within 0.001 of DKKM. FMR overflows in 0.8% of months (extreme raw levels).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BGN</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>regime-g extreme (g0235)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0.1859500600381938</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0.1351606914149408</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.1584490887927846</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.0232883973778438</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.0673657426503773</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0.0903648568677055</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.145497914042626</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0.1751691825010399</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.0296712684584139</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>29.10917580346855</v>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Regime multipliers pushed to [0.2, 3.5], near the closed-form frontier. Room saturates (+0.023, same as [0.3,3.0]) but the realized gap GROWS: +0.030 over the best linear and +0.108 over FMR (t=29) - the wilder regime breaks rolling FMR/FF/linlev while DKKM's rank features are immune. Largest relative gap of the project (~160% over FMR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>KP</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>priced-vol extreme (vyx)</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1.260673206906341</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.7425929743612978</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>1.092156653947947</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0.3495636795866488</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.7408015545124442</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0.6470108495345773</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.7475352995906872</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.8484250537647645</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0.1008897541740773</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>21.58900016720147</v>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>kp_vy pushed to gamma_v=1.8, beta=[0.02,0.07,0.14] (premia ~6/15/28%/yr). Room +0.350 (largest of project) AND capture jumps from ~10% to ~29%: rff_ens 0.848 vs FMR 0.741 - gap +0.108 (t=21.6), +0.101 over the best linear. The data-magnitude KP win; stronger cross-sectional signal lifts both room and capture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>exposure-types extreme (bx9)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>0.323435912401572</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.2569683254597307</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.310929588176601</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0.0539612627168702</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0.1870954457836175</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>0.2024044218368605</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>0.2097125068262536</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.2089667910182114</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>-0.0007457158080421</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>5.076777106067119</v>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>5 types beta 1-9, harsher regime [0.5,4.0]. Room triples to +0.054 but the harvest COLLAPSES: linrank 0.210 ~ rff 0.209 (DKKM edge over linear gone; both beat FMR by ~+0.022, t~5). The wilder economy inflates theta-estimation noise faster than the room grows - GS's harvest frontier at T=360 is the bx7 calibration.</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1558,12 +1821,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>column</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>definition</t>
         </is>
@@ -1575,7 +1838,7 @@
           <t>model</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Structural model: BGN (Berk-Green-Naik 1999), KP (Kogan-Papanikolaou 2014), GS (Gomes-Schmid 2021).</t>
         </is>
@@ -1587,7 +1850,7 @@
           <t>variant</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Economy variant; see the description column and REPORT.md.</t>
         </is>
@@ -1599,7 +1862,7 @@
           <t>SR_max</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Mean conditional maximum Sharpe ratio of the economy (population, monthly).</t>
         </is>
@@ -1611,7 +1874,7 @@
           <t>lin_ceil</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Best population constant-theta ceiling over linear bases (rank chars, +regime feature, +levels).</t>
         </is>
@@ -1623,7 +1886,7 @@
           <t>nl_ceil</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Best population constant-theta ceiling over nonlinear bases (RFF up to P=3600, poly2, bins).</t>
         </is>
@@ -1635,7 +1898,7 @@
           <t>room</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>nl_ceil - lin_ceil: population Sharpe available to nonlinear methods beyond any linear method.</t>
         </is>
@@ -1647,7 +1910,7 @@
           <t>FMR</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Best realized mean conditional SR, Fama-MacBeth regression portfolios (raw chars, rolling 360m MVE).</t>
         </is>
@@ -1659,7 +1922,7 @@
           <t>FF</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Best realized SR, Fama-French sorted factor portfolios (rolling 360m MVE).</t>
         </is>
@@ -1671,7 +1934,7 @@
           <t>lin</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Best realized SR over linear methods: ridge on rank chars (linrank) or ranks+levels (linlev).</t>
         </is>
@@ -1683,7 +1946,7 @@
           <t>RFF</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Best realized SR over DKKM variants: random-Fourier-feature ridge (rff, rff_ens, rff_lev, rff_lev_ens), kappa grid to 10.</t>
         </is>
@@ -1695,7 +1958,7 @@
           <t>gap_RFF-lin</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>RFF - lin: realized nonlinear-over-linear gap.</t>
         </is>
@@ -1707,7 +1970,7 @@
           <t>t_vs_FMR</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Paired monthly t-statistic of the best RFF variant's conditional SR against FMR.</t>
         </is>
